--- a/outputs/essay3_q2/ADJUDICATION.xlsx
+++ b/outputs/essay3_q2/ADJUDICATION.xlsx
@@ -11,6 +11,7 @@
     <sheet name="round1_v1" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="round2_v2" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="flagged_by_reference" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="audit_v2" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -591,10 +592,8 @@
           <t>v1 (d39bc6d)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -663,10 +662,8 @@
           <t>v1 (d39bc6d)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C3" t="n">
+        <v>7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -739,10 +736,8 @@
           <t>v1 (d39bc6d)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C4" t="n">
+        <v>14</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -811,10 +806,8 @@
           <t>v1 (d39bc6d)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="C5" t="n">
+        <v>21</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -887,10 +880,8 @@
           <t>v1 (d39bc6d)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C6" t="n">
+        <v>27</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -963,10 +954,8 @@
           <t>v1 (d39bc6d)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="C7" t="n">
+        <v>31</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1039,10 +1028,8 @@
           <t>v1 (d39bc6d)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="C8" t="n">
+        <v>32</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1111,10 +1098,8 @@
           <t>v1 (d39bc6d)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="C9" t="n">
+        <v>37</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1183,10 +1168,8 @@
           <t>v1 (d39bc6d)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="C10" t="n">
+        <v>39</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1255,10 +1238,8 @@
           <t>v1 (d39bc6d)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="C11" t="n">
+        <v>52</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1323,10 +1304,8 @@
           <t>v1 (d39bc6d)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="C12" t="n">
+        <v>53</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1399,10 +1378,8 @@
           <t>v1 (d39bc6d)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+      <c r="C13" t="n">
+        <v>58</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1475,10 +1452,8 @@
           <t>v1 (d39bc6d)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="C14" t="n">
+        <v>62</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1547,10 +1522,8 @@
           <t>v1 (d39bc6d)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="C15" t="n">
+        <v>63</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1623,10 +1596,8 @@
           <t>v1 (d39bc6d)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="C16" t="n">
+        <v>66</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1695,10 +1666,8 @@
           <t>v1 (d39bc6d)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="C17" t="n">
+        <v>71</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1771,10 +1740,8 @@
           <t>v1 (d39bc6d)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="C18" t="n">
+        <v>76</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2410,10 +2377,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="A2" t="n">
+        <v>57</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -2471,10 +2436,8 @@
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="A3" t="n">
+        <v>16</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -2534,4 +2497,2010 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>round</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>classifier</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sheet_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>filing_date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>treated</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>fields_in_dispute</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>classifier_codes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>blind</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>restates_prior_disclosure</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>reference_person</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>classifier_person</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>reference_note</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>text_excerpt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>adjudicated_exec (Y/N)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>adjudicated_ceo (Y/N)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>adjudicated_director_only (Y/N)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>adjudicated_pre_announced (Y/N/unclear)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>adjudicator</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>adjudication_note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sprint Nextel</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/101830/000119312520093630/d853508d8k.htm</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ceo_departure, director_only_departure, pre_announced</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=Y / dir=Y / pre=Y</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=Y / pre=unclear</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Executives: Raul Marcelo Claure (Executive Chairman), Michel Combes (President and CEO), Nestor Cano (COO), John Saw (CTO), Andrew Davies (CFO), Jorge Gracia (CLO), Paul Schieber (VP and Controller). Directors only: Bethune, Doyle, Fisher, Genachowski, Kappes, Mullen, Son, Tucker</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Paul Schieber (PAO: Vice President Controller)</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Transaction-driven (T-Mobile/Sprint close, 2020-04-01). BLIND pre-announced = unclear (Business Combination Agreement cited, undated). VERIFIED: the agreement is dated 2018-04-29, before the reference date; primary = Y.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>In accordance with the terms of the Business Combination Agreement, at the Effective Time, J. Braxton Carter and David A. Miller, who were the directors of Merger Sub immediately prior to the Effective Time, became directors of Sprint. In addition, in accordance with the Business Combination Agreement, effective as of the Effective Time, Gordon M. Bethune, Raul Marcelo Claure, Michel Combes, Patrick T. Doyle, Ronald D. Fisher, Julius Genachowski, Stephen R. Kappes, Admiral Michael G. Mullen, Masayoshi Son and Sara Martinez Tucker are no longer directors of Sprint; in each case, this cessation of service was not related to any disagreement with Sprint on any matter relating to Sprint’s operations, policies or practices. As of the Effective Time, G. Michael Sievert, Mr. Carter and Peter Osvaldik became the Chief Executive Officer &amp; President, Executive Vice President &amp; Chief Financial Officer, and Senior Vice President, Finance &amp; Chief Accounting Officer, respectively, of Sprint. In connection therewith, as of the Effective Time, Mr. Claure, Executive Chairman, Mr. Combes, President and Chief Executive Officer, Nestor Cano, Chief Operating Officer, John Saw, Chief Technology Officer, Andrew Davies, Chief Financial Officer, Jorge Gracia, Chief Legal Officer, and Paul Schieber, Vice President and Controller, no longer serve in such positions for Sprint; in each case, this cessation of service was not related to any disagreement with Sprint on any matter relating to Sprint’s opera</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Carnival Corporation</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2022-04-27</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/815097/000110465922051225/tm2213670d1_8k.htm</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>exec_departure, ceo_departure</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=Y / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>exec=unclear / ceo=unclear / pre=N</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Arnold Donald, President and CEO (becomes Vice Chair)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>BLIND: exec/CEO = unclear; the Item 5.02 text only points to Exhibit 99.1. VERIFIED from the filing's own Ex. 99.1 (2022-04-26): Donald leaves President and CEO effective 2022-08-01. Primary = Y. STRUCTURAL: the departure appears only in the exhibit, which a classifier reading the Item 5.02 section cannot see.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Carnival Corporation and Carnival plc have announced senior executive transitions, described in greater detail in the attached press release included as Exhibit 99.1. Compensation for each person is still under consideration and will be reported once finalized. The information set forth in Exhibit 99.1 is incorporated herein by reference.</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Adobe Systems Incorporated</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2014-01-29</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/796343/000079634314000007/a8-kxitem502xjanuary2014.htm</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>exec_departure, pre_announced</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / dir=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / pre=unclear</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Kevin Lynch (no longer with the Company; former EVP and CTO)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Background mention in a compensation filing. BLIND pre-announced = unclear (no departure date in text). VERIFIED: Lynch resigned 2013-03-18, effective 2013-03-22, before reference date; primary = Y.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>(e) 2014 Performance Share Program On January 24, 2014, the Executive Compensation Committee (the “Committee”) of the Board of Directors (the “Board”) of Adobe Systems Incorporated (“Adobe” or the “Company”) approved the 2014 Performance Share Program, including the Award Calculation Methodology (the “Program”), under the terms of the Company’s 2003 Equity Incentive Plan. The Committee established the Program to help focus key employees on building stockholder value, provide significant award potential for achieving outstanding Company performance, and enhance the ability of the Company to attract and retain highly talented and competent individuals. Members of the Company’s executive management team and other key members of senior management were selected by the Committee to participate in the Program for fiscal year 2014. The Committee granted awards for the executive officers under the Program on January 24, 2014 in the form of a target award and a maximum award of performance shares (“Performance Shares”) approved pursuant to the terms of the Company’s 2003 Equity Incentive Plan. Under our Performance Share Program for fiscal year 2014, shares may be earned based on the achievement of objective relative total stockholder return (“TSR”) measured over a three-year performance period (Adobe’s 2014 - 2016 fiscal years). Three years following the date of grant, the Committee will certify the performance results and the number of Performance Shares earned as of the end of the t</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AT&amp;T</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2020-04-28</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/732717/000119312520123202/d913267d8k.htm</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ceo_departure, pre_announced</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=Y / dir=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=Y / pre=Y</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Randall Stephenson, CEO (becomes Executive Chairman; retiring January 2021)</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Randall Stephenson (other_exec: Executive Chairman of the Board)</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Board action 2020-04-23, before reference date.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>On April 23, 2020, the Board of Directors (the “Board”) of AT&amp;T Inc. (the “Company”) adopted a resolution that effective June 1, 2020, the size of the Board would increase from 13 to 14 members and John Stankey, the Company’s President and Chief Operating Officer, would be elected a Director to fill the resulting vacancy. Mr. Stankey will not receive any separate compensation for his service as a Director of the Company. In addition, effective July 1, 2020, the Board appointed Mr. Stankey to be Chief Executive Officer and President and Randall Stephenson to be Executive Chairman of the Board. Mr. Stephenson announced his intention to serve as Executive Chairman of the Board until his retirement from the Company in January 2021. John Stankey, age 57, has served as President and COO of AT&amp;T Inc. since October 2019, overseeing AT&amp;T Communications, WarnerMedia, and Xandr. Since June 2018, he has led WarnerMedia, which creates premium content, operates the world’s largest TV and film studio, and owns a world-class library of entertainment. Mr. Stankey has held various roles during his 33 years of service with the Company, including CEO-AT&amp;T Entertainment Group; Chief Strategy Officer; President and CEO of AT&amp;T Business Solutions; President and CEO of AT&amp;T Operations; Group President-Telecom Operations; Chief Technology Officer; and Chief Information Officer.</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>American Electric Power</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2019-09-18</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/4904/000000490419000042/a09-20198xkitem502dire.htm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>director_only_departure</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / dir=Y / pre=N</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / pre=N</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Art Garcia (director: director)</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Director election; the retirement mentioned is from another company.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>On September 17, 2019, the Board of Directors (the “Board”) of American Electric Power Company, Inc. (the “Company”) elected Art Garcia to serve as a director of the Company. Mr. Garcia’s initial term as a director will continue until the 2020 annual meeting of shareholders. The Board appointed Mr. Garcia to the Audit Committee, the Committee on Directors and Corporate Governance (“Corporate Governance Committee”), the Finance Committee and the Policy Committee. Mr. Garcia retired from Ryder System, Inc. (“Ryder”), effective April 30, 2019. He served as Executive Vice-President and Chief Financial Officer of Ryder from September 2010 to April 2019. Mr. Garcia serves as a director of ABM Industries Inc. and Elanco Animal Health Inc. The Board has determined that Mr. Garcia is an “independent” director under the Company’s Principles of Corporate Governance and the independence requirements of the New York Stock Exchange, as well as the applicable rules promulgated by the Securities and Exchange Commission. As a non-employee director, Mr. Garcia will receive the same compensation paid to other non-employee directors of the Company in accordance with the policies and procedures previously approved by the Board for non-employee directors.</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise Company</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2023-12-15</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1645590/000164559023000110/hpe-20231213.htm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>pre_announced</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>exec=unclear / ceo=N / dir=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>exec=unclear / ceo=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Jeremy K. Cox, Interim CFO and Principal Financial Officer (stays as SVP, Controller, PAO)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Interim title, not covered by the rules. Dates before the reference date if counted.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On December 13, 2023, the Board of Directors (the “Board”) of Hewlett Packard Enterprise Company (“HPE” or the “Company”) appointed Marie Myers to serve as HPE's Executive Vice President and Chief Financial Officer, effective as of January 15, 2024 (the “Effective Date”). In this capacity, Ms. Myers will also serve as the Company's Principal Financial Officer as of the Effective Date. Jeremy K. Cox will continue to serve as Interim Chief Financial Officer and Principal Financial Officer of HPE until the Effective Date, after which, he will continue to serve as HPE's Senior Vice President, Corporate Controller, Chief Tax Officer and Principal Accounting Officer. Ms. Myers, 55, has served as the Chief Financial Officer of HP Inc. (“HP”), a global information technology company, since February 2021, where she leads the company's finance organization and has been responsible for all aspects of financial operations. Previously, she served in numerous other leadership positions at HP: Interim Chief Financial Officer from October 2020 to February 2021, Chief Transformation Officer from June 2020 to February 2021, and Chief Digital Officer from March 2020 to October 2020. Prior to that, she served as Chief Financial Officer of UiPath, Inc., a robotic process automation company, from December 2018 to December 2019. From December 2015 to December 2018, Ms. Myers served as Global Controller of HP, and prior to that, she held numerous positions within the audit and finance organizations </t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AT&amp;T</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2019-09-06</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/732717/000119312519239966/d799915d8k.htm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>exec_departure, pre_announced</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / dir=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>John Donovan, CEO of AT&amp;T Communications, LLC (subsidiary CEO, not principal executive officer)</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Restates the 2019-08-26 disclosure; before reference date.</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>As previously disclosed by AT&amp;T Inc. on August 26, 2019, John Donovan, Chief Executive Officer of AT&amp;T Communications, LLC, announced he was leaving the company effective October 1, 2019. On September 3, 2019, Mr. Donovan entered into an Agreement and Release and Waiver of Claims (the “Agreement”). Pursuant to the terms of the Agreement: • Mr. Donovan will receive a cash payment of $7,850,000. • Mr. Donovan’s restricted stock granted in 2015 will vest upon his leaving the company on October 1, 2019. • Beginning October 2, 2019, Mr. Donovan will provide consulting services for one year for an aggregate fee of $2,800,000. The Agreement also includes a release and waiver of claims by Mr. Donovan and contains various covenants, including restrictive covenants relating to non-competition, non-solicitation and confidentiality. The foregoing summary of the Agreement does not purport to be complete and is qualified in its entirety by reference to the Agreement, which is filed as Exhibit 10.1 and is incorporated herein by reference.</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>21</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sprint Nextel</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2016-05-06</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/101830/000010183016000063/a8-k20160503.htm</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>director_only_departure, pre_announced</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / dir=Y / pre=Y</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Robert Bennett, director</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Notice 2016-05-03, before reference date.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>On May 3, 2016, Robert Bennett notified Sprint Corporation (the “Company”) that he would not stand for re-election to the Company’s board of directors at its next annual meeting. Mr. Bennett’s decision was not a result of any disagreement with the Company.</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>22</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>GoDaddy.com LLC</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1609711/000160971121000059/gddy-20210501.htm</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>exec_departure, pre_announced</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / dir=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Mr. Winborne, CFO and principal financial officer (serves until 2021-06-02)</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Implied departure: successor appointed with a stated end date for the incumbent, no departure verb. Appointment 2021-05-01, before reference date.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>(c) Appointment of Chief Financial Officer On May 1, 2021, the board of directors of the Company (the "Board") appointed Mark D. McCaffrey to serve as the Company’s Chief Financial Officer and principal financial officer, effective June 2, 2021 (the "CFO Effective Date"). Mr. Winborne will continue to serve as the Company’s Chief Financial Officer and principal financial officer until the CFO Effective Date. On May 1, 2021, the Company and certain of its affiliates entered into an employment letter with Mr. McCaffrey, effective as of the CFO Effective Date (the "McCaffrey Employment Letter"). The McCaffrey Employment Letter does not have a specific term and provides that Mr. McCaffrey’s employment will be at-will. The McCaffrey Employment Letter provides Mr. McCaffrey with an annual base salary of $525,000 and an opportunity to earn an annual incentive bonus of 80% of his base salary, which will be pro-rated for fiscal 2021 beginning on the CFO Effective Date. In addition, Mr. McCaffrey will receive a signing bonus of $250,000, payable in the first pay period after the CFO Effective Date. If his employment ends within one year of the CFO Effective Date as a result of a termination of his employment for cause or his resignation without good reason (both terms as defined in the McCaffrey Employment Letter), he will be required to return a pro-rated portion of the net-after tax amount of the signing bonus, as determined in accordance with the McCaffrey Employment Letter. Pursuan</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AT&amp;T</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2022-08-04</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/732717/000073271722000091/t-20220630.htm</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>pre_announced</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>exec=unclear / ceo=N / dir=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>exec=unclear / ceo=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Pascal Desroches, Senior EVP and CFO (no longer principal accounting officer)</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Designation transfer only; he keeps his office. Not covered by the rules.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>On June 30, 2022, AT&amp;T Inc., a Delaware corporation (the “Company”), appointed Debra L. Dial to the position of Senior Vice President - Chief Accounting Officer and Controller, and Ms. Dial assumed the responsibilities of principal accounting officer. Ms. Dial, 61, has served in various positions with the Company for 25 years, including as Senior Vice President - Controller for the last six years. The designation as the principal accounting officer recognizes her responsibilities as Chief Accounting Officer and conforms to prevalent industry practice. Pascal Desroches, the Company's Senior Executive Vice President and Chief Financial Officer, acted as the Company's principal accounting officer prior to Ms. Dial's appointment. 3 Signature Pursuant to the requirements of the Securities Exchange Act of 1934, the Registrant has duly caused this report to be signed on its behalf by the undersigned hereunto duly authorized. AT&amp;T INC. /s/ Stacey Maris Date: August 4, 2022 Stacey Maris Senior Vice President - Deputy General Counsel and Secretary 4</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>27</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ServiceNow Inc.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1373715/000137371524000269/now-20240724.htm</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>pre_announced</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / dir=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / pre=N</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Chirantan 'CJ' Desai, President and COO</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Mr. Desai (COO: President and Chief Operating Officer)</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Resigned 2024-07-24, after reference date. Text states a policy violation found by an internal investigation.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On July 24, 2024, the Company and its President and Chief Operating Officer, Chirantan “CJ” Desai, came to a mutual agreement that Mr. Desai would resign from all positions with the Company, effective immediately. As previously referenced in the Company’s Form 10-Q for the quarter ended March 31, 2024, through its internal processes, the Company received a complaint that raised potential compliance issues related to one of its government contracts. The Company initiated an internal investigation, with the assistance of outside legal counsel, into the validity of these claims that concern the hiring of the Chief Information Officer of the U.S. Army as the Company’s Head of Global Public Sector in March 2023. As a result of the investigation, the Company’s Board of Directors (the “Board”) determined that Mr. Desai and the hired individual violated Company policy regarding a possible conflict relating to such individual’s hiring. Mr. Desai has fully cooperated with the investigation and maintains that he did not intentionally violate Company policy. The other individual also has departed the Company. The Company has informed the Department of Justice, the Department of Defense Office of Inspector General and the Army Suspension and Debarment Office of the investigation and is continuing to cooperate with the Department of Justice, which has commenced its own investigation into these matters. The Company cannot predict the timing, outcome or possible impact of the investigation. </t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>29</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sprint Nextel</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2009-03-27</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/101830/000010183009000007/k2009march27hockaday.txt</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>director_only_departure, pre_announced</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / dir=Y / pre=Y</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Irvine O. Hockaday Jr., director</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Notice 2009-03-23, before reference date.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>(b) On March 23, 2009, Irvine O. Hockaday, Jr. notified Sprint Nextel Corporation (the "Company") that he has decided not to stand for re-election at the next annual meeting of stockholders to be held May 12, 2009. His decision is not as the result of any disagreement with the Company on any matter relating to the Company's operations, policies or practices.</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>34</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Hewlett-Packard Company</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2006-09-12</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/47217/000110465906060568/a06-19530_18k.htm</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>exec_departure</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / dir=Y / pre=Y</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / dir=Y / pre=Y</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>George A. Keyworth II, director</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Patricia C. Dunn (other_exec: executive Chairman of the Board of Directors); Keyworth II (director: director); Dr. Keyworth (director: Board)</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Patricia Dunn gives up the non-executive chair but stays a director, so she is not coded. Dates before reference date.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>(b) On September 12, 2006, Patricia C. Dunn resigned as non-executive Chairman of the Board of Directors of Hewlett-Packard Company (“HP”) effective at the adjournment of the regularly scheduled meeting of the Board of Directors of HP to be held on January 18, 2007. At that time, Mark V. Hurd, Chief Executive Officer and President of HP, will assume the additional role of Chairman of the Board, and Richard A. Hackborn, a member of the HP Board since 1992, will become HP’s lead independent director. Ms. Dunn will continue to serve as a director following the effective time of her resignation as Chairman. The text of HP’s press release entitled “Patricia Dunn to Remain HP Chairman Through January 2007 Board Meeting; Board Appoints Mark Hurd As Successor” is filed with this report as Exhibit 99.1. Also on September 12, 2006, Dr. George A. Keyworth II resigned as a director of HP, effective immediately. Dr. Keyworth has confirmed to the HP Board that his resignation is not the result of any disagreement on any matter relating to HP’s operations, policies or practices.</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>39</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>T-Mobile USA, Inc.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2016-06-22</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1283699/000119312516628913/d386854d8k.htm</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>exec_departure, pre_announced</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / dir=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Michael J. Morgan, SVP Finance and Chief Accounting Officer (moves to a new role)</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Leaves the PAO title while staying employed. Effective 2016-06-20, before reference date.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(b) Effective as of June 20, 2016, Michael J. Morgan, who previously served as Senior Vice President, Finance &amp; Chief Accounting Officer of T-Mobile US, Inc. (the “Company”), transitioned into a new position with the Company and will serve as the Company’s Senior Vice President — Finance, Customer Financial Services and will oversee the Company’s Financial Services team that develops and supports our core consumer financing products. Mr. Morgan will continue to report to J. Braxton Carter, Executive Vice President and Chief Financial Officer. (c) Effective as of June 20, 2016, Peter Osvaldik was appointed Senior Vice President, Finance &amp; Chief Accounting Officer of the Company. Mr. Osvaldik, 39, previously served as Vice President, External Reporting &amp; Technical Accounting of the Company since January 2016. From May 2014 to December 2015, he served as Chief Accounting Officer at Outerwall Inc. (formerly known as Coinstar, Inc.), a provider of automated retail solutions, including movie and video game rental kiosks as well as coin-counting kiosks. Prior to that, he served in various capacities at Outerwall, Inc., including as Controller, Coinstar LOB, the automated coin-counting business of Outerwall, from November 2010 to February 2013 and as Corporate Controller from February 2013 to May 2014. Prior to joining Outerwall, Mr. Osvaldik was a Senior Manager at PricewaterhouseCoopers LLP, a national public accounting firm. Mr. Osvaldik received a Bachelor’s degree in Accounting </t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>40</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2012-11-01</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/8670/000117184312003874/document.htm</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>exec_departure, pre_announced</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / dir=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Christopher Reidy, CFO</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Announced 2012-11-01, before reference date.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>(b) On November 1, 2012, Automatic Data Processing, Inc. (the "Company") announced that the Company and Christopher Reidy have mutually agreed that Mr. Reidy would no longer serve as Chief Financial Officer of the Company after November 2, 2012. Mr. Reidy will remain available through calendar year-end to facilitate an orderly transition of his responsibilities to his successor. (c) On November 1, 2012, the Company announced that Jan Siegmund, the Company's Chief Strategy Officer and President, Added Value Services, has been appointed Chief Financial Officer of the Company, effective November 5, 2012. Mr. Siegmund, who is 48 years old, joined the Company in 1999 as Vice President of Corporate Strategy and has held increasingly senior executive leadership positions since that time. Prior to his promotion, he served as both Chief Strategy Officer, with overall responsibility for the Company's strategy, product management, marketing and corporate development, as well as President of the Added Value Services division, overseeing tax, compliance services and insurance services. He assumed these positions in 2009 and 2007, respectively. Prior to these roles, Mr. Siegmund served as the Company's Corporate Vice President, Strategic Development from 2004 to 2007 and as Senior Vice President of Strategic Development, Brokerage Services at the Company's Brokerage Services Group from 2000 to 2004.</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>47</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Intuit, Inc.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2008-02-08</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/896878/000095013408001977/f37812e8vk.htm</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>exec_departure, pre_announced</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / dir=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>exec=unclear / ceo=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Jeffrey E. Stiefler (SVP, Financial Institutions Division, per verification)</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>BLIND: exec = unclear (text gives no title). VERIFIED: SVP, Financial Institutions Division; executive-officer status not confirmed. Primary = Y, flagged for adjudication. Agreement 2008-02-04, before reference date.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>On February 4, 2008, Intuit Inc. and Jeffrey E. Stiefler entered into a Separation Terms and General Release Agreement (the “Agreement”), under which Mr. Stiefler’s employment with Intuit will terminate on February 15, 2008 and he will provide services as a consultant through July 2008. In exchange for his waiver and release of claims in favor of the company, Mr. Stiefler will receive accelerated vesting of 40,000 restricted stock units and a one-time payment of $45,000 for continuing healthcare premiums. The Agreement has been filed as an exhibit to this report on Form 8-K, and becomes irrevocable 7 days from February 4, 2008. The above description is qualified in its entirety by reference to the Separation Terms and General Release Agreement which is filed as Exhibit 10.01 to this report on Form 8-K.</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>48</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Honeywell International Inc.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2021-07-14</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/773840/000119312521215278/d153129d8k.htm</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ceo_departure</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=Y / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / pre=N</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Rajeev Gautam, President and CEO, Performance Materials and Technologies segment (segment CEO)</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Rajeev Gautam (CEO: President and Chief Executive Officer); Rajeev Gautam (CEO: President Chief Executive Officer); Rajeev Gautam (CEO: President Chief Executive Officer)</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Notice 2021-07-14, after reference date.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>On July 14, 2021, Rajeev Gautam, President and Chief Executive Officer of the Performance Materials and Technologies segment (“PMT”) of Honeywell International Inc. (the “Company”), communicated his intent to retire from the Company effective as of August 13, 2021 (the “Retirement Date”). Following the Retirement Date and through the end of January 2022, Mr. Gautam will serve as President Emeritus, Honeywell PMT, with responsibility for ensuring smooth customer transitions across PMT and helping enable growth within the Honeywell UOP business unit. Mr. Vimal Kapur, age 55, has been appointed to succeed Mr. Gautam as President and Chief Executive Officer of PMT. Mr. Kapur has served since May 2018 as President and Chief Executive Officer of the Honeywell Building Technologies segment (“HBT”), and prior to that, Mr. Kapur led PMT’s Honeywell Process Solutions business (“HPS”) from 2014 to 2018. In addition, Mr. Kapur has held several other leadership positions at Honeywell, including Vice President and General Manager of the Advanced Solutions line of business for HPS and Managing Director for Honeywell Automation India Limited (HAIL). Mr. Doug Wright, age 51, has been appointed to succeed Mr. Kapur as President and Chief Executive Officer of HBT. Mr. Wright has served as President of HBT’s Fire and Security business since joining the Company in July 2020. Before joining the Company, Mr. Wright served from 2013 to 2020 as President and Chief Executive Officer of Source Photonic</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>51</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Charter Communications, Inc.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2008-07-08</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1091667/000109166708000143/body.htm</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>director_only_departure</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / dir=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / dir=Y / pre=Y</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Robert A. Quigley, EVP and Chief Marketing Officer</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>None (director: DIRECTORS OR CERTAIN OFFICERS; ELECTION OF DIRECTORS); Robert A. Quigley (other_exec: Executive Vice President and Chief Marketing Officer)</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>'As previously announced'; resignation effective 2008-07-01, before reference date.</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>DEPARTURE OF CERTAIN DIRECTORS OR CERTAIN OFFICERS; ELECTION OF DIRECTORS; APPOINTMENT OF CERTAIN OFFICERS; COMPENSATORY ARRANGEMENTS OF CERTAIN OFFICERS. On July 1, 2008, as previously announced by Charter Communications, Inc. ("Charter") in a Form 8-K filed on June 23, 2008, Eloise E. Schmitz became the Executive Vice President and Chief Financial Officer of Charter. As of July 1, Ms. Schmitz's annual base salary increased to $525,000 and she received grants of 92,593 shares of restricted stock, 108,932 performance units and $100,000 in performance cash pursuant to the terms of Charter's 2008 Incentive Program. In addition, her annual bonus target under Charter's Executive Bonus Plan will be 75% of her annual base salary. It is anticipated that Ms. Schmitz will enter into an amended and restated employment agreement, the terms of which will include the above-referenced terms; additional terms included in Charter's employment agreements with Executive Vice Presidents include that in the event of a termination by Charter without cause or by Ms. Schmitz for Good Reason (as defined in the employment agreement), Charter shall pay her two times her annual base salary and a lump sum equal to 24 months of COBRA payments (compared to the one year payments in the current agreement). Also, on July 1, 2008, as previously announced, Robert A. Quigley resigned as Executive Vice President and Chief Marketing Officer, although he will remain as an advisor to Charter and retire at the end o</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>55</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Verizon</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2013-06-10</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/732712/000119312513253564/d551901d8k.htm</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>pre_announced</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>exec=unclear / ceo=N / dir=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>exec=N / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>exec=unclear / ceo=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Robert J. Barish, SVP and Controller (succeeded; stays leading FP&amp;A)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Implied departure from the Controller title; the text does not say Controller is the principal accounting officer. Dates before reference date if counted.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Effective June 10, 2013, Anthony T. Skiadas, 44, became Senior Vice President and Controller of Verizon Communications Inc. (Verizon). Mr. Skiadas has held high-level managerial positions in the finance organization of Verizon and its subsidiaries over the past five years. He succeeds Robert J. Barish, who will continue to lead the corporate financial planning and analysis organization.</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>57</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CenturyLink</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2013-03-25</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/18926/000119312513124519/d509961d8k.htm</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ceo_departure</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / dir=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=Y / dir=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>James E. Ousley, CEO, Savvis Operations (segment CEO)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>James E. Ousley (CEO: Chief Executive Officer); James E. Ousley (CEO: Chief Executive Officer)</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Filed under (b). Filing predates reference date.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>(b) James E. Ousley, Chief Executive Officer, Savvis Operations, will retire effective April 1, 2013. A press release announcing his retirement is attached as Exhibit 99.1.</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>70</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DISH Network, LLC</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1001082/000110465923116755/tm2323753d3_8k.htm</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>pre_announced</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=Y / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=Y / dir=N / pre=unclear</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=Y / pre=unclear</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>W. Erik Carlson, President and CEO (stays on board through merger)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Mr. Carlson (CEO: President and Chief Executive Officer)</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>BLIND pre-announced = unclear ('previously disclosed', no date). VERIFIED: notice 2023-11-03 (DISH 8-K), after reference date; primary = N.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>On November 9, 2023, DISH Network Corporation (“DISH”) appointed Mr. Hamid Akhavan, the current Chief Executive Officer and President of EchoStar Corporation (“EchoStar”), to the additional role of President and Chief Executive Officer of DISH effective as of November 13, 2023. As previously disclosed, Mr. Carlson notified DISH of his intention to resign as President and Chief Executive Officer of DISH effective as of November 12, 2023, but will remain on the board of directors of DISH (the “DISH Board”) through the closing of the previously announced merger between DISH and EchoStar (the “Merger”). The appointment of Mr. Akhavan was approved by a special committee of independent directors of the DISH Board (the “DISH Special Committee”), subject to the approval of the DISH Board, and was subsequently approved by the DISH Board. The approval of the DISH Board was conditioned upon the approval of the board of directors of EchoStar (the “EchoStar Board”) of a compensation sharing agreement between DISH and EchoStar, which approval was obtained on November 9, 2023. Mr. Akhavan will retain his current position as Chief Executive Officer and President of EchoStar. Prior to joining EchoStar on March 31, 2022, Mr. Akhavan served as a Partner at Twin Point Capital, an investment firm, beginning in April 2018, and from March 2016 to April 2018, he was a Founding Partner of Long Arc Capital LLC. Prior to March 2016, Mr. Akhavan held a variety of leadership positions, including as Chief</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>71</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Verizon</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/732712/000119312517303383/d469226d8k.htm</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ceo_departure</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=Y / dir=N / pre=N</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / pre=N</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Marni M. Walden, EVP and President, Global Media</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Lowell McAdam (CEO: Chief Executive Officer)</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Announced by the 2017-10-04 filing, after reference date.</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Verizon Communications Inc. announced that Marni M. Walden, Verizon’s Executive Vice President and President – Global Media, would step down from her current position effective at the close of business on December 31, 2017. Following that date, she will report to Lowell McAdam, the Chairman and Chief Executive Officer of Verizon, as a strategic advisor and will leave the company in February 2018.</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>v2 (6f7be7a)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>75</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>T-Mobile USA, Inc.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2018-04-30</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1283699/000110465918028086/a18-12444_18k.htm</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>reference unclear</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=unclear / dir=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=N / dir=N / pre=Y</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>exec=Y / ceo=unclear / pre=Y</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>John J. Legere, President (title passes to Sievert 2018-04-29; employment term set to end 2020-04-30, 'unless earlier terminated'); J. Braxton Carter, EVP and CFO (term extended to a transaction-contingent end date)</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>John J. Legere (president: President upon ratification by the T-Mobile board of directors); Michael Sievert (COO: Chief Operating Officer)</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>CEO coded unclear: the amendment sets an end date for Legere's employment, but it is a term extension, not framed as a departure. The President title change is coded as an executive departure (same rule as round-1 Southwest/Kelly). 2018-04-29, before reference date. See chat note on first-disclosure dating.</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">. Executive Severance Letters On April 27, 2018, the compensation committee of the board of directors of T-Mobile approved the entry into severance letter agreements (the “Letter Agreements”) with each of J. Braxton Carter, T-Mobile’s Executive Vice President and Chief Financial Officer, Neville R. Ray, T-Mobile’s Executive Vice President and Chief Technology Officer, and Thomas C. Keys, T-Mobile’s President, MetroPCS (collectively, the “Executives”), which became effective on April 29, 2018. Each Letter Agreement provides that, upon a termination of the applicable Executive’s employment by T-Mobile without “cause” or by the Executive for “good reason” (each as defined in the applicable Letter Agreement) (each, a “qualifying termination”) in either case, within twelve (12) months following the first to occur of (i) the closing of the Transactions or (ii) the date on which T-Mobile publicly announces that the Transactions will not close, and subject to the Executive’s timely execution and non-revocation of a release of claims in favor of T-Mobile and continued compliance with certain non-competition and non-solicitation restrictions for eighteen (18) months following such qualifying termination (or, if such qualifying termination occurs within twelve (12) months following the date on which T-Mobile publicly announces that the Transactions will not close, twelve (12) months), the Executive will receive: · a lump-sum payment equal to two (2) times the sum of (I) the Executive’s </t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>